--- a/artfynd/A 55725-2023 artfynd.xlsx
+++ b/artfynd/A 55725-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55725-2023 artfynd.xlsx
+++ b/artfynd/A 55725-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>79258126</v>
       </c>
       <c r="B2" t="n">
-        <v>96356</v>
+        <v>98102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421458.4385687422</v>
+        <v>421458</v>
       </c>
       <c r="R2" t="n">
-        <v>6467636.136894612</v>
+        <v>6467636</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,19 +760,9 @@
           <t>2019-08-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -812,7 +802,7 @@
         <v>79643725</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
+        <v>97999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420807.2138873882</v>
+        <v>420807</v>
       </c>
       <c r="R3" t="n">
-        <v>6467611.367441055</v>
+        <v>6467611</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +868,9 @@
           <t>2015-07-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 55725-2023 artfynd.xlsx
+++ b/artfynd/A 55725-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 55725-2023 artfynd.xlsx
+++ b/artfynd/A 55725-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 55725-2023 artfynd.xlsx
+++ b/artfynd/A 55725-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>79258126</v>
       </c>
       <c r="B2" t="n">
-        <v>98124</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,12 +797,7 @@
         <v>79643725</v>
       </c>
       <c r="B3" t="n">
-        <v>98021</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
